--- a/output/casestudy_20260827.xlsx
+++ b/output/casestudy_20260827.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>10.61634520000007</v>
+        <v>8.412770899998577</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>10.0784165999994</v>
+        <v>9.134801500000322</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>5.782039100000475</v>
+        <v>5.582604300001549</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>10.22965769999973</v>
+        <v>9.751138899999205</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>11.11217380000016</v>
+        <v>10.3814069</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>7.175320500000453</v>
+        <v>6.603703299999324</v>
       </c>
     </row>
   </sheetData>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10.6 초</t>
+          <t>8.4 초</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.1 초</t>
+          <t>9.1 초</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5.8 초</t>
+          <t>5.6 초</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10.2 초</t>
+          <t>9.8 초</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11.1 초</t>
+          <t>10.4 초</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7.2 초</t>
+          <t>6.6 초</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>56.7 초</t>
+          <t>51.0 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260827.xlsx
+++ b/output/casestudy_20260827.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>8.412770899998577</v>
+        <v>10.10192169999937</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>9.134801500000322</v>
+        <v>10.23116880000089</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>5.582604300001549</v>
+        <v>6.135194900001807</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>9.751138899999205</v>
+        <v>10.98276979999719</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>10.3814069</v>
+        <v>12.03197530000034</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>6.603703299999324</v>
+        <v>7.396276199997374</v>
       </c>
     </row>
   </sheetData>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8.4 초</t>
+          <t>10.1 초</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>9.1 초</t>
+          <t>10.2 초</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5.6 초</t>
+          <t>6.1 초</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.8 초</t>
+          <t>11.0 초</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10.4 초</t>
+          <t>12.0 초</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6.6 초</t>
+          <t>7.4 초</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>51.0 초</t>
+          <t>58.1 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260827.xlsx
+++ b/output/casestudy_20260827.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>10.10192169999937</v>
+        <v>9.984758800001146</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>10.23116880000089</v>
+        <v>9.779945400001452</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>6.135194900001807</v>
+        <v>5.924539399999048</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>10.98276979999719</v>
+        <v>10.83600260000094</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>12.03197530000034</v>
+        <v>11.46282649999921</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>7.396276199997374</v>
+        <v>7.121657700001379</v>
       </c>
     </row>
   </sheetData>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10.1 초</t>
+          <t>10.0 초</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.2 초</t>
+          <t>9.8 초</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6.1 초</t>
+          <t>5.9 초</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11.0 초</t>
+          <t>10.8 초</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12.0 초</t>
+          <t>11.5 초</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7.4 초</t>
+          <t>7.1 초</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>58.1 초</t>
+          <t>56.3 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260827.xlsx
+++ b/output/casestudy_20260827.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>9.984758800001146</v>
+        <v>10.35590509999747</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>9.779945400001452</v>
+        <v>10.01506069999959</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>5.924539399999048</v>
+        <v>6.103172899998754</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>10.83600260000094</v>
+        <v>9.58216320000065</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>11.46282649999921</v>
+        <v>10.82299599999897</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>7.121657700001379</v>
+        <v>7.181534200000897</v>
       </c>
     </row>
   </sheetData>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10.0 초</t>
+          <t>10.4 초</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>9.8 초</t>
+          <t>10.0 초</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5.9 초</t>
+          <t>6.1 초</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10.8 초</t>
+          <t>9.6 초</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11.5 초</t>
+          <t>10.8 초</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7.1 초</t>
+          <t>7.2 초</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>56.3 초</t>
+          <t>55.2 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260827.xlsx
+++ b/output/casestudy_20260827.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>10.35590509999747</v>
+        <v>11.22784590000083</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>10.01506069999959</v>
+        <v>11.30795440000293</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>6.103172899998754</v>
+        <v>7.082834400000138</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>9.58216320000065</v>
+        <v>11.21998869999879</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>10.82299599999897</v>
+        <v>12.22170059999917</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>7.181534200000897</v>
+        <v>8.723791899999924</v>
       </c>
     </row>
   </sheetData>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10.4 초</t>
+          <t>11.2 초</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.0 초</t>
+          <t>11.3 초</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6.1 초</t>
+          <t>7.1 초</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.6 초</t>
+          <t>11.2 초</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10.8 초</t>
+          <t>12.2 초</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7.2 초</t>
+          <t>8.7 초</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>55.2 초</t>
+          <t>63.1 초</t>
         </is>
       </c>
     </row>
